--- a/eventos/sap-bdc-innovation-day-2026/SAP_BDC_Innovation_Day_2026_Checklist.xlsx
+++ b/eventos/sap-bdc-innovation-day-2026/SAP_BDC_Innovation_Day_2026_Checklist.xlsx
@@ -230,6 +230,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="008B0000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="007B5800"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF3CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="001A5C2A"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00CCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -678,7 +719,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
@@ -706,7 +747,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr"/>
@@ -734,7 +775,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -762,7 +803,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr"/>
@@ -790,7 +831,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
@@ -818,7 +859,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr"/>
@@ -846,7 +887,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr"/>
@@ -874,7 +915,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr"/>
@@ -909,7 +950,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -937,7 +978,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
@@ -965,7 +1006,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -993,7 +1034,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
@@ -1021,7 +1062,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -1049,7 +1090,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr"/>
@@ -1077,7 +1118,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -1105,7 +1146,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr"/>
@@ -1133,7 +1174,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
@@ -1161,7 +1202,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr"/>
@@ -1189,7 +1230,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
@@ -1217,7 +1258,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr"/>
@@ -1245,7 +1286,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
@@ -1273,7 +1314,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
@@ -1301,7 +1342,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr"/>
@@ -1329,7 +1370,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr"/>
@@ -1357,7 +1398,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr"/>
@@ -1392,7 +1433,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
@@ -1420,7 +1461,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr"/>
@@ -1448,7 +1489,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1476,7 +1517,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr"/>
@@ -1504,7 +1545,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1532,7 +1573,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr"/>
@@ -1560,7 +1601,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1588,7 +1629,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
@@ -1616,7 +1657,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1644,7 +1685,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr"/>
@@ -1672,7 +1713,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1707,7 +1748,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1735,7 +1776,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr"/>
@@ -1763,7 +1804,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1791,7 +1832,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
@@ -1819,7 +1860,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1847,7 +1888,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr"/>
@@ -1875,7 +1916,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -1903,7 +1944,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr"/>
@@ -1938,7 +1979,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -1966,7 +2007,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr"/>
@@ -1994,7 +2035,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2022,7 +2063,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr"/>
@@ -2050,7 +2091,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2078,7 +2119,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr"/>
@@ -2106,7 +2147,7 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2134,7 +2175,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr"/>
@@ -2162,7 +2203,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2190,7 +2231,7 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr"/>
@@ -2218,7 +2259,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2246,7 +2287,7 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr"/>
@@ -2281,7 +2322,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2309,7 +2350,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr"/>
@@ -2337,7 +2378,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2365,7 +2406,7 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr"/>
@@ -2393,7 +2434,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2421,7 +2462,7 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr"/>
@@ -2449,7 +2490,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2477,7 +2518,7 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr"/>
@@ -2505,7 +2546,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2533,7 +2574,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr"/>
@@ -2561,7 +2602,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2589,7 +2630,7 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr"/>
@@ -2617,7 +2658,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2645,7 +2686,7 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr"/>
@@ -2661,6 +2702,22 @@
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A53:F53"/>
   </mergeCells>
+  <conditionalFormatting sqref="E5:E80">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E5="Pendente"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$E5="Em andamento"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$E5="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Escolha: Pendente, Em andamento ou OK" type="list">
+      <formula1>"Pendente,Em andamento,OK"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2748,7 +2805,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2828,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2851,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2874,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2897,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2927,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2950,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2973,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2996,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3019,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2992,7 +3049,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3072,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3095,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3118,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3141,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3164,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3194,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3217,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3240,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3270,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3293,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3316,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3339,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3296,6 +3353,22 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
+  <conditionalFormatting sqref="E5:E32">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E5="Pendente"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$E5="Em andamento"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$E5="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Escolha: Pendente, Em andamento ou OK" type="list">
+      <formula1>"Pendente,Em andamento,OK"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3384,7 +3457,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3489,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3521,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3553,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3585,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3617,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3681,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3713,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>A fazer</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -3648,6 +3721,22 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <conditionalFormatting sqref="F4:F12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F4="Pendente"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$F4="Em andamento"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$F4="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F4:F12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Escolha: Pendente, Em andamento ou OK" type="list">
+      <formula1>"Pendente,Em andamento,OK"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/eventos/sap-bdc-innovation-day-2026/SAP_BDC_Innovation_Day_2026_Checklist.xlsx
+++ b/eventos/sap-bdc-innovation-day-2026/SAP_BDC_Innovation_Day_2026_Checklist.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,12 @@
       <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -92,7 +98,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +118,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4F4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -166,19 +177,22 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,10 +201,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -199,28 +213,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -717,7 +731,7 @@
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -725,22 +739,22 @@
       <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Definir nome definitivo do evento</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
@@ -750,7 +764,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -773,7 +787,7 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -781,22 +795,22 @@
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Confirmar speakers e apresentadores internos</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Sócios</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
@@ -806,7 +820,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -829,7 +843,7 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -837,22 +851,22 @@
       <c r="F10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Confirmar participação de especialistas SAP para demo</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
@@ -862,7 +876,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -885,7 +899,7 @@
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -893,22 +907,22 @@
       <c r="F12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Segmentar lista por perfil (MQL, prospect, cliente ativo)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
@@ -918,7 +932,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -948,7 +962,7 @@
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -956,22 +970,22 @@
       <c r="F15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Produzir card WhatsApp do evento</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Fran / Design</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
@@ -981,7 +995,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1004,7 +1018,7 @@
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1012,22 +1026,22 @@
       <c r="F17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Redigir e-mail 02 — 2º convite</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
@@ -1037,7 +1051,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1060,7 +1074,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1068,22 +1082,22 @@
       <c r="F19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Redigir e-mail 04 — 4º convite</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>08/08/2026</t>
         </is>
@@ -1093,7 +1107,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1116,7 +1130,7 @@
           <t>15/08/2026</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1124,22 +1138,22 @@
       <c r="F21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Redigir lembrete D-2</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>22/08/2026</t>
         </is>
@@ -1149,7 +1163,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1172,7 +1186,7 @@
           <t>25/08/2026</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1180,22 +1194,22 @@
       <c r="F23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Criar anúncios LinkedIn — formato 1200x1200 (mín. 4 versões)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Fran / Design</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
@@ -1205,7 +1219,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1228,7 +1242,7 @@
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1236,22 +1250,22 @@
       <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Preparar apresentação abertura + BDC</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Sócios / Consultores</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>18/08/2026</t>
         </is>
@@ -1261,7 +1275,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr"/>
+      <c r="F26" s="9" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -1284,7 +1298,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1292,22 +1306,22 @@
       <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Criar QR Code da pesquisa de satisfação (Qualtrics)</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
@@ -1317,7 +1331,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -1340,7 +1354,7 @@
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1348,22 +1362,22 @@
       <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Produzir posts pós-evento</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Fran / Design</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>25/08/2026</t>
         </is>
@@ -1373,7 +1387,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -1396,7 +1410,7 @@
           <t>22/08/2026</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1431,7 +1445,7 @@
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1439,22 +1453,22 @@
       <c r="F33" s="6" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Ativar LinkedIn Ads — campanha de convite</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
@@ -1464,7 +1478,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -1487,7 +1501,7 @@
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1495,22 +1509,22 @@
       <c r="F35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Disparar E-mail 02 — 2º convite</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
@@ -1520,7 +1534,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -1543,7 +1557,7 @@
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1551,22 +1565,22 @@
       <c r="F37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Disparo WhatsApp para base qualificada</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>30/07 – 04/08</t>
         </is>
@@ -1576,7 +1590,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -1599,7 +1613,7 @@
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1607,22 +1621,22 @@
       <c r="F39" s="6" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Período RSVP — confirmação de presença</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>11/08 – 22/08</t>
         </is>
@@ -1632,7 +1646,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -1655,7 +1669,7 @@
           <t>18/08/2026</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1663,22 +1677,22 @@
       <c r="F41" s="6" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Publicar post de contagem regressiva</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
@@ -1688,7 +1702,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -1711,7 +1725,7 @@
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1746,7 +1760,7 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1754,22 +1768,22 @@
       <c r="F45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Comprar brindes — Moleskine e Caneta (70 unidades)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
@@ -1779,7 +1793,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr"/>
+      <c r="F46" s="9" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -1802,7 +1816,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1810,22 +1824,22 @@
       <c r="F47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Reservar equipamento — projetor, áudio, tela</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>SAP Brasil / Fran</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
@@ -1835,7 +1849,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr"/>
+      <c r="F48" s="9" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -1858,7 +1872,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1866,22 +1880,22 @@
       <c r="F49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Verificar disponibilidade da sala Experience para demo complementar</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
@@ -1891,7 +1905,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr"/>
+      <c r="F50" s="9" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -1914,7 +1928,7 @@
           <t>19/08/2026</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1922,22 +1936,22 @@
       <c r="F51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Montar plano de contingência (speaker, internet, coffee)</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>19/08/2026</t>
         </is>
@@ -1947,7 +1961,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr"/>
+      <c r="F52" s="9" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -1977,7 +1991,7 @@
           <t>26/08 — 07:30</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1985,22 +1999,22 @@
       <c r="F54" s="6" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Testar projetor, áudio e internet</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>26/08 — 07:45</t>
         </is>
@@ -2010,7 +2024,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -2033,7 +2047,7 @@
           <t>26/08 — 07:50</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2041,22 +2055,22 @@
       <c r="F56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Confirmar brindes disponíveis na recepção</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>26/08 — 08:00</t>
         </is>
@@ -2066,7 +2080,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -2089,7 +2103,7 @@
           <t>26/08 — 08:00</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2097,22 +2111,22 @@
       <c r="F58" s="6" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Definir quem faz credenciamento</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>26/08 — 08:00</t>
         </is>
@@ -2122,7 +2136,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr"/>
+      <c r="F59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -2145,7 +2159,7 @@
           <t>26/08 — 08:30</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2153,22 +2167,22 @@
       <c r="F60" s="6" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Registrar presença dos participantes</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>26/08 — durante</t>
         </is>
@@ -2178,7 +2192,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -2201,7 +2215,7 @@
           <t>26/08 — durante</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2209,22 +2223,22 @@
       <c r="F62" s="6" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>Identificar e abordar leads quentes em tempo real</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Sócios</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>26/08 — durante</t>
         </is>
@@ -2234,7 +2248,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr"/>
+      <c r="F63" s="9" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -2257,7 +2271,7 @@
           <t>26/08 — após</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2265,22 +2279,22 @@
       <c r="F64" s="6" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Distribuir brindes mediante QR Code da pesquisa</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>26/08 — durante/encerramento</t>
         </is>
@@ -2290,7 +2304,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -2320,7 +2334,7 @@
           <t>27/08/2026</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2328,22 +2342,22 @@
       <c r="F67" s="6" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>Publicar post pós-evento LinkedIn + Instagram</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>27/08/2026</t>
         </is>
@@ -2353,7 +2367,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr"/>
+      <c r="F68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -2376,7 +2390,7 @@
           <t>29/08/2026</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2384,22 +2398,22 @@
       <c r="F69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>Limpar e deduplicar dados de leads</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>29/08/2026</t>
         </is>
@@ -2409,7 +2423,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr"/>
+      <c r="F70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -2432,7 +2446,7 @@
           <t>29/08/2026</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2440,22 +2454,22 @@
       <c r="F71" s="6" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>Classificar leads: Quente / Morno / Frio</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Fran + Sócios</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>29/08/2026</t>
         </is>
@@ -2465,7 +2479,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr"/>
+      <c r="F72" s="9" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -2488,7 +2502,7 @@
           <t>29/08/2026</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2496,22 +2510,22 @@
       <c r="F73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>Follow-up D+1 — contato direto com leads quentes</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Comercial</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>27/08/2026</t>
         </is>
@@ -2521,7 +2535,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr"/>
+      <c r="F74" s="9" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -2544,7 +2558,7 @@
           <t>29/08/2026</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2552,22 +2566,22 @@
       <c r="F75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>Follow-up D+5 — ligação comercial para SQLs</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Comercial</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
@@ -2577,7 +2591,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr"/>
+      <c r="F76" s="9" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -2600,7 +2614,7 @@
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2608,22 +2622,22 @@
       <c r="F77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>Gerar relatório de resultados (leads, pipeline, ROI)</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
@@ -2633,7 +2647,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr"/>
+      <c r="F78" s="9" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -2656,7 +2670,7 @@
           <t>01-12/09/2026</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2664,22 +2678,22 @@
       <c r="F79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>Registrar aprendizados para próxima edição</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Fran + Sócios</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
@@ -2689,7 +2703,7 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2787,18 +2801,18 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Confirmar espaço SAP Brasil</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
@@ -2826,25 +2840,25 @@
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Confirmar case e speakers</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Fran / Sócios</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
@@ -2872,25 +2886,25 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Comprar brindes</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
@@ -2925,25 +2939,25 @@
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Montar lista de convidados segmentada</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
@@ -2971,25 +2985,25 @@
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>E-mail 02 — 2º convite</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
@@ -3017,7 +3031,7 @@
           <t>30/07 – 04/08</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -3031,18 +3045,18 @@
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>E-mail 03 — 3º convite</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
@@ -3070,25 +3084,25 @@
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Período RSVP / confirmações</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>11/08 – 22/08</t>
         </is>
@@ -3116,25 +3130,25 @@
           <t>18/08/2026</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr"/>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Preparação final (materiais, brindes, lista)</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>25/08/2026</t>
         </is>
@@ -3162,7 +3176,7 @@
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -3176,18 +3190,18 @@
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="8" t="inlineStr"/>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Execução do evento</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Fran + Sócios</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>26/08/2026</t>
         </is>
@@ -3215,25 +3229,25 @@
           <t>26/08/2026</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr"/>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Cobertura foto/vídeo (Stories/Reels)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>26/08/2026</t>
         </is>
@@ -3268,25 +3282,25 @@
           <t>27/08/2026</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr"/>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Consolidar leads no HubSpot</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>29/08/2026</t>
         </is>
@@ -3314,25 +3328,25 @@
           <t>27/08 – 03/09</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr"/>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr"/>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Relatório de resultados</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
@@ -3435,7 +3449,7 @@
           <t>☐</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>E-mail 01 — 1º Convite</t>
         </is>
@@ -3455,34 +3469,34 @@
           <t>&gt;20%</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>E-mail 02 — 2º Convite</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Reforço — destacar speakers e case</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>&gt;15%</t>
         </is>
@@ -3499,7 +3513,7 @@
           <t>☐</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>E-mail 03 — 3º Convite</t>
         </is>
@@ -3519,34 +3533,34 @@
           <t>&gt;18%</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>E-mail 04 — 4º Convite</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Última chamada geral</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>&gt;14%</t>
         </is>
@@ -3563,7 +3577,7 @@
           <t>☐</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>E-mail 05 — RSVP</t>
         </is>
@@ -3583,34 +3597,34 @@
           <t>&gt;20%</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Lembrete D-2</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Lembrete final para confirmados</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>&gt;30%</t>
         </is>
@@ -3627,7 +3641,7 @@
           <t>☐</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Agradecimento pós-evento</t>
         </is>
@@ -3647,34 +3661,34 @@
           <t>&gt;40%</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Confirmação de inscrição</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Confirmar cadastro e fornecer detalhes</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>&gt;40%</t>
         </is>
@@ -3691,7 +3705,7 @@
           <t>☐</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Recebimento de inscrição</t>
         </is>
@@ -3711,7 +3725,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -3766,7 +3780,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Budget total: R$ 6.000,00</t>
         </is>
@@ -3831,30 +3845,30 @@
       <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Brindes — Moleskine + Caneta (70 un.)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>R$ 800,00</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Condicionado ao QR Code da pesquisa</t>
         </is>
@@ -3891,101 +3905,101 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Contingência (10%)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Reserva inclusa no coffee (10% a mais contratado)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>R$ 6.000,00</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Custo por inscrito esperado (120 inscrições):</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>~R$ 50,00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Custo por participante esperado (70 presentes):</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>~R$ 86,00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Custo por oportunidade esperado (6 deals):</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>~R$ 1.000,00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr"/>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Referência fev/2025: R$ 5.034,80 investidos → 5 deals → ROI 9.824%</t>
         </is>
@@ -4058,17 +4072,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Inscrições</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>120</t>
         </is>
@@ -4081,40 +4095,40 @@
       <c r="E5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Participantes</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Não participaram</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -4127,40 +4141,40 @@
       <c r="E7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Taxa de comparecimento</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>≥ 58%</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>MQLs</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -4173,40 +4187,40 @@
       <c r="E9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>SQLs</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Oportunidades (deals)</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4219,40 +4233,40 @@
       <c r="E11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Pipeline gerado</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>~R$ 2,5M</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>R$ 3.000.000</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Investimento total</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>R$ 5.034,80</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>R$ 6.000,00</t>
         </is>
@@ -4265,40 +4279,40 @@
       <c r="E13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>9.824%</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>&gt;9.000%</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Custo por inscrito</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>R$ 46,62</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>~R$ 50,00</t>
         </is>
@@ -4311,40 +4325,40 @@
       <c r="E15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Custo por participante</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>R$ 79,92</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>~R$ 86,00</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Custo por oportunidade</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>R$ 1.006,96</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>~R$ 1.000,00</t>
         </is>
@@ -4357,27 +4371,27 @@
       <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Tx. abertura e-mail média</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>~19%</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>&gt;20%</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -4387,7 +4401,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>O que funcionou:</t>
         </is>
@@ -4395,7 +4409,7 @@
       <c r="B22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>O que não funcionou:</t>
         </is>
@@ -4403,7 +4417,7 @@
       <c r="B23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>O que melhorar:</t>
         </is>
@@ -4411,7 +4425,7 @@
       <c r="B24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Próximos passos:</t>
         </is>

--- a/eventos/sap-bdc-innovation-day-2026/SAP_BDC_Innovation_Day_2026_Checklist.xlsx
+++ b/eventos/sap-bdc-innovation-day-2026/SAP_BDC_Innovation_Day_2026_Checklist.xlsx
@@ -55,7 +55,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="008B0000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -98,7 +97,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -118,11 +117,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4F4F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -177,19 +171,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,13 +222,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -249,12 +243,12 @@
       <font>
         <name val="Calibri"/>
         <b val="1"/>
-        <color rgb="008B0000"/>
+        <color rgb="001A5C2A"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFCCCC"/>
+          <fgColor rgb="00CCFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -275,12 +269,12 @@
       <font>
         <name val="Calibri"/>
         <b val="1"/>
-        <color rgb="001A5C2A"/>
+        <color rgb="008B0000"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00CCFFCC"/>
+          <fgColor rgb="00FFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2717,14 +2711,14 @@
     <mergeCell ref="A53:F53"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E80">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E5="Pendente"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>$E5="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$E5="Em andamento"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$E5="OK"</formula>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>$E5="Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3368,14 +3362,14 @@
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E32">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E5="Pendente"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>$E5="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$E5="Em andamento"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$E5="OK"</formula>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>$E5="Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3736,14 +3730,14 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:F12">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F4="Pendente"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>$F4="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>$F4="Em andamento"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$F4="OK"</formula>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>$F4="Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
